--- a/Climber/敵座標.xlsx
+++ b/Climber/敵座標.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KudoSyota\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KudoSyota\Documents\GitHub\WinterGame2025\Climber\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DFFA4991-8541-424E-AED8-205F97D86B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C82526C0-A00C-4965-9B1B-C1B53A45A848}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" xr2:uid="{D313FE66-75BD-43B2-A26C-31A429F37DC7}"/>
+    <workbookView xWindow="2865" yWindow="-15900" windowWidth="21600" windowHeight="11295" xr2:uid="{D313FE66-75BD-43B2-A26C-31A429F37DC7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="33">
   <si>
     <t>敵の場所</t>
     <rPh sb="0" eb="1">
@@ -57,10 +57,6 @@
   </si>
   <si>
     <t>コウモリ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ウサギ</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -78,6 +74,103 @@
       <t>ヨ</t>
     </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>うさぎ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>X</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>47~753</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>端から端</t>
+    <rPh sb="0" eb="1">
+      <t>ハジ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ハジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>b10-&gt;Init();</t>
+  </si>
+  <si>
+    <t>b10-&gt;SetPos({ 53,159422 });</t>
+  </si>
+  <si>
+    <t>m_pBats.push_back(b10);</t>
+  </si>
+  <si>
+    <t>auto b10 = std::make_shared&lt;Bat&gt;();</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>b11-&gt;Init();</t>
+  </si>
+  <si>
+    <t>m_pBats.push_back(b11);</t>
+  </si>
+  <si>
+    <t>auto b12 = std::make_shared&lt;Bat&gt;();</t>
+  </si>
+  <si>
+    <t>b12-&gt;Init();</t>
+  </si>
+  <si>
+    <t>m_pBats.push_back(b12);</t>
+  </si>
+  <si>
+    <t>auto b11 = std::make_shared&lt;Bat&gt;();</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>b11-&gt;SetPos({ 53,159423 });</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>b11-&gt;SetPos({ 53,159424 });</t>
+  </si>
+  <si>
+    <t>auto b13 = std::make_shared&lt;Bat&gt;();</t>
+  </si>
+  <si>
+    <t>b13-&gt;Init();</t>
+  </si>
+  <si>
+    <t>b11-&gt;SetPos({ 53,159425 });</t>
+  </si>
+  <si>
+    <t>m_pBats.push_back(b13);</t>
+  </si>
+  <si>
+    <t>auto b14 = std::make_shared&lt;Bat&gt;();</t>
+  </si>
+  <si>
+    <t>b14-&gt;Init();</t>
+  </si>
+  <si>
+    <t>b11-&gt;SetPos({ 53,159426 });</t>
+  </si>
+  <si>
+    <t>m_pBats.push_back(b14);</t>
+  </si>
+  <si>
+    <t>auto b15 = std::make_shared&lt;Bat&gt;();</t>
+  </si>
+  <si>
+    <t>b15-&gt;Init();</t>
+  </si>
+  <si>
+    <t>b11-&gt;SetPos({ 53,159427 });</t>
+  </si>
+  <si>
+    <t>m_pBats.push_back(b15);</t>
   </si>
 </sst>
 </file>
@@ -461,15 +554,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26CA5220-2FCF-4C6D-ADB4-1018DFF5E5E2}">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:O40"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.4">
       <c r="B2" t="s">
         <v>1</v>
       </c>
@@ -477,139 +570,294 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3">
-        <v>337</v>
-      </c>
       <c r="C3">
-        <v>159282</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+        <v>159422</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>159245</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>158520</v>
+      </c>
+      <c r="H5" t="s">
         <v>4</v>
       </c>
-      <c r="B4">
-        <v>319</v>
-      </c>
-      <c r="C4">
-        <v>158577</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5">
-        <v>297</v>
-      </c>
-      <c r="C5">
-        <v>157906</v>
-      </c>
-      <c r="H5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6">
-        <v>321</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>157425</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+        <v>157265</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>3</v>
       </c>
-      <c r="B7">
-        <v>495</v>
-      </c>
       <c r="C7">
-        <v>157225</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+        <v>155744</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8">
-        <v>301</v>
+        <v>3</v>
       </c>
       <c r="C8">
-        <v>156721</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+        <v>155744</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>3</v>
       </c>
-      <c r="B9">
-        <v>401</v>
-      </c>
       <c r="C9">
-        <v>156228</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+        <v>155181</v>
+      </c>
+      <c r="I9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>3</v>
       </c>
-      <c r="B10">
-        <v>527</v>
-      </c>
       <c r="C10">
-        <v>149571</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+        <v>152397</v>
+      </c>
+      <c r="H10" t="s">
+        <v>8</v>
+      </c>
+      <c r="I10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11">
-        <v>641</v>
+        <v>3</v>
       </c>
       <c r="C11">
-        <v>150193</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+        <v>152111</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>3</v>
       </c>
-      <c r="B12">
-        <v>321</v>
-      </c>
       <c r="C12">
-        <v>150626</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>3</v>
       </c>
-      <c r="B13">
-        <v>303</v>
-      </c>
       <c r="C13">
-        <v>151129</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>3</v>
       </c>
-      <c r="B14">
-        <v>463</v>
-      </c>
       <c r="C14">
-        <v>151773</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="O16" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="O17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="B18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" t="s">
+        <v>2</v>
+      </c>
+      <c r="O18" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19">
+        <v>593</v>
+      </c>
+      <c r="C19">
+        <v>154705</v>
+      </c>
+      <c r="O19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20">
+        <v>253</v>
+      </c>
+      <c r="C20">
+        <v>154641</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21">
+        <v>305</v>
+      </c>
+      <c r="C21">
+        <v>152721</v>
+      </c>
+      <c r="O21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>5</v>
+      </c>
+      <c r="O22" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>5</v>
+      </c>
+      <c r="O23" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>5</v>
+      </c>
+      <c r="O24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>5</v>
+      </c>
+      <c r="O25" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>5</v>
+      </c>
+      <c r="O26" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A27" t="s">
+        <v>5</v>
+      </c>
+      <c r="O27" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
+        <v>5</v>
+      </c>
+      <c r="O28" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A29" t="s">
+        <v>5</v>
+      </c>
+      <c r="O29" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A30" t="s">
+        <v>5</v>
+      </c>
+      <c r="O30" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="O31" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="O32" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33" spans="15:15" x14ac:dyDescent="0.4">
+      <c r="O33" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="15:15" x14ac:dyDescent="0.4">
+      <c r="O34" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="15:15" x14ac:dyDescent="0.4">
+      <c r="O35" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36" spans="15:15" x14ac:dyDescent="0.4">
+      <c r="O36" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="37" spans="15:15" x14ac:dyDescent="0.4">
+      <c r="O37" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="38" spans="15:15" x14ac:dyDescent="0.4">
+      <c r="O38" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39" spans="15:15" x14ac:dyDescent="0.4">
+      <c r="O39" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="40" spans="15:15" x14ac:dyDescent="0.4">
+      <c r="O40" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
